--- a/TestData.xlsx
+++ b/TestData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t xml:space="preserve">TestName</t>
   </si>
@@ -140,6 +140,15 @@
   </si>
   <si>
     <t xml:space="preserve">Password-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ram.rajpal@bitsinglass.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appian@24</t>
   </si>
 </sst>
 </file>
@@ -505,7 +514,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.27"/>
@@ -590,7 +599,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.27"/>
@@ -675,7 +684,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.94"/>
@@ -738,8 +747,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C1048576"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
@@ -779,11 +788,26 @@
         <v>38</v>
       </c>
     </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="Rules@123456"/>
     <hyperlink ref="B3" r:id="rId2" display="prashant.todmal@bitsinglass.com"/>
     <hyperlink ref="C3" r:id="rId3" display="Password-1"/>
+    <hyperlink ref="B4" r:id="rId4" display="ram.rajpal@bitsinglass.com"/>
+    <hyperlink ref="C4" r:id="rId5" display="Appian@24"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
